--- a/结果/Q4_结果.xlsx
+++ b/结果/Q4_结果.xlsx
@@ -492,11 +492,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S011,S015</t>
+          <t>S001,S004,S005,S006,S007,S010</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -505,7 +505,7 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -514,10 +514,10 @@
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -531,11 +531,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S002,S004,S008,S009,S010,S012,S013,S014</t>
+          <t>S002,S003,S008,S009,S011,S012,S013,S014,S015</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -544,13 +544,13 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -570,11 +570,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S011,S015</t>
+          <t>S001,S003,S006,S007,S011,S015</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -583,7 +583,7 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -609,32 +609,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S002,S004,S013</t>
+          <t>S002,S004,S005,S009,S010,S013</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -648,7 +648,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S008,S009,S010,S012,S014</t>
+          <t>S008,S012,S014</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -782,7 +782,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
     </row>
@@ -850,26 +850,26 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" t="n">
         <v>6</v>
       </c>
-      <c r="E3" t="n">
-        <v>5</v>
-      </c>
       <c r="F3" t="n">
-        <v>0.0643</v>
+        <v>0.1082</v>
       </c>
       <c r="G3" t="n">
-        <v>1.138</v>
+        <v>1.243</v>
       </c>
       <c r="H3" t="n">
-        <v>6.5</v>
+        <v>82.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/6</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -894,17 +894,17 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>5/4</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>3/2</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
     </row>
@@ -921,19 +921,19 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7635</v>
+        <v>0.7873</v>
       </c>
       <c r="G4" t="n">
-        <v>7.455</v>
+        <v>8.401999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>6.5</v>
+        <v>2590.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>5/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
     </row>
@@ -986,22 +986,22 @@
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0011</v>
+        <v>0.0018</v>
       </c>
       <c r="G5" t="n">
-        <v>1.002</v>
+        <v>1.004</v>
       </c>
       <c r="H5" t="n">
-        <v>6.5</v>
+        <v>82.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -1010,37 +1010,37 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>3/2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>3/2</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>6/6</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>5/4</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>4/2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>3/2</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>6/6</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>7/4</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>5/4</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>4/2</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
     </row>
@@ -1054,22 +1054,22 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D6" t="n">
+        <v>13</v>
+      </c>
+      <c r="E6" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="n">
-        <v>7</v>
-      </c>
       <c r="F6" t="n">
-        <v>0.1563</v>
+        <v>0.1982</v>
       </c>
       <c r="G6" t="n">
-        <v>1.387</v>
+        <v>1.641</v>
       </c>
       <c r="H6" t="n">
-        <v>6.5</v>
+        <v>109.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1078,14 +1078,14 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>4/2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>3/2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>3/2</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>6/6</t>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>5/4</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>5/4</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
@@ -1131,13 +1131,13 @@
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9809</v>
+        <v>0.8699</v>
       </c>
       <c r="G7" t="n">
-        <v>8.528</v>
+        <v>7.53</v>
       </c>
       <c r="H7" t="n">
-        <v>3504.6</v>
+        <v>2590.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1146,37 +1146,37 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>3/2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>3/2</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>7/6</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>4/2</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>6/6</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>5/4</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>4/2</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
     </row>
@@ -1190,61 +1190,61 @@
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E8" t="n">
         <v>17</v>
       </c>
-      <c r="E8" t="n">
-        <v>14</v>
-      </c>
       <c r="F8" t="n">
-        <v>0.0216</v>
+        <v>0.0156</v>
       </c>
       <c r="G8" t="n">
-        <v>1.05</v>
+        <v>1.038</v>
       </c>
       <c r="H8" t="n">
-        <v>6.5</v>
+        <v>109.6</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>7/4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>3/2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>6/2</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>8/6</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5/4</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>6/4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>5/2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>4/2</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>6/2</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>6/6</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>6/4</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>6/4</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>5/2</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>5/6</t>
         </is>
       </c>
     </row>
@@ -1349,46 +1349,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>33.181</v>
+        <v>26.308</v>
       </c>
       <c r="H2" t="n">
-        <v>1.343</v>
+        <v>2.791</v>
       </c>
       <c r="I2" t="n">
-        <v>21160.4</v>
+        <v>16121.8</v>
       </c>
       <c r="J2" t="n">
-        <v>4710.6</v>
+        <v>10033</v>
       </c>
       <c r="K2" t="n">
-        <v>25871</v>
+        <v>26154.9</v>
       </c>
       <c r="L2" t="n">
-        <v>7130.3</v>
+        <v>6560</v>
       </c>
       <c r="M2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Q3-T02,Q3-T04,Q3-T07,Q3-T09,Q3-T10,Q3-T12,Q3-T13,Q3-T14,Q3-T15,Q3-T16,Q3-T19,Q3-T21</t>
+          <t>Q3-T03,Q3-T07,Q3-T08,Q3-T09,Q3-T10,Q3-T11,Q3-T17,Q3-T19,Q3-T21</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R01,Q3-R02,Q3-R03</t>
         </is>
       </c>
     </row>
@@ -1402,46 +1402,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>32.283</v>
+        <v>37.985</v>
       </c>
       <c r="H3" t="n">
-        <v>2.83</v>
+        <v>2.326</v>
       </c>
       <c r="I3" t="n">
-        <v>19274.8</v>
+        <v>24269.9</v>
       </c>
       <c r="J3" t="n">
-        <v>10153.5</v>
+        <v>8232.200000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>29428.3</v>
+        <v>32502.2</v>
       </c>
       <c r="L3" t="n">
-        <v>7136.8</v>
+        <v>6477.2</v>
       </c>
       <c r="M3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Q3-T01,Q3-T03,Q3-T05,Q3-T06,Q3-T08,Q3-T11,Q3-T17,Q3-T18,Q3-T20,Q3-T22</t>
+          <t>Q3-T01,Q3-T02,Q3-T04,Q3-T05,Q3-T06,Q3-T12,Q3-T13,Q3-T14,Q3-T15,Q3-T16,Q3-T18,Q3-T20</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Q3-R01,Q3-R02,Q3-R03</t>
+          <t>Q3-R01,Q3-R02</t>
         </is>
       </c>
     </row>
@@ -1455,41 +1455,41 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>33.181</v>
+        <v>26.164</v>
       </c>
       <c r="H4" t="n">
-        <v>1.343</v>
+        <v>1.224</v>
       </c>
       <c r="I4" t="n">
-        <v>21160.4</v>
+        <v>16674</v>
       </c>
       <c r="J4" t="n">
-        <v>4710.6</v>
+        <v>4321.8</v>
       </c>
       <c r="K4" t="n">
-        <v>25871</v>
+        <v>20995.8</v>
       </c>
       <c r="L4" t="n">
-        <v>7130.3</v>
+        <v>6477.2</v>
       </c>
       <c r="M4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Q3-T02,Q3-T04,Q3-T07,Q3-T09,Q3-T10,Q3-T12,Q3-T13,Q3-T14,Q3-T15,Q3-T16,Q3-T19,Q3-T21</t>
+          <t>Q3-T03,Q3-T06,Q3-T07,Q3-T08,Q3-T10,Q3-T11,Q3-T12,Q3-T15,Q3-T20</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1508,41 +1508,41 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>17.707</v>
+        <v>27.477</v>
       </c>
       <c r="H5" t="n">
-        <v>2.83</v>
+        <v>2.791</v>
       </c>
       <c r="I5" t="n">
-        <v>8495.1</v>
+        <v>16053.5</v>
       </c>
       <c r="J5" t="n">
-        <v>10153.5</v>
+        <v>10033</v>
       </c>
       <c r="K5" t="n">
-        <v>18648.6</v>
+        <v>26086.5</v>
       </c>
       <c r="L5" t="n">
-        <v>7136.8</v>
+        <v>6560</v>
       </c>
       <c r="M5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Q3-T01,Q3-T03,Q3-T08,Q3-T20</t>
+          <t>Q3-T01,Q3-T02,Q3-T04,Q3-T09,Q3-T13,Q3-T17,Q3-T19,Q3-T21</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1561,41 +1561,41 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>14.576</v>
+        <v>10.652</v>
       </c>
       <c r="H6" t="n">
-        <v>2.337</v>
+        <v>2.326</v>
       </c>
       <c r="I6" t="n">
-        <v>10779.7</v>
+        <v>7664.3</v>
       </c>
       <c r="J6" t="n">
-        <v>8278.5</v>
+        <v>8232.200000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>19058.2</v>
+        <v>15896.5</v>
       </c>
       <c r="L6" t="n">
-        <v>7130.3</v>
+        <v>6450.4</v>
       </c>
       <c r="M6" t="n">
         <v>9</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Q3-T05,Q3-T06,Q3-T11,Q3-T17,Q3-T18,Q3-T22</t>
+          <t>Q3-T05,Q3-T14,Q3-T16,Q3-T18</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1615,7 +1615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1671,27 +1671,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A型运输无人机</t>
+          <t>B型运输无人机</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>G1需4，G2需2</t>
+          <t>G1需1，G2需2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B型运输无人机</t>
+          <t>C型运输无人机</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>G1需1，G2需2</t>
+          <t>G1需2，G2需1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1741,17 +1741,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C型运输无人机</t>
+          <t>A型电池组</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>G1需2，G2需1</t>
+          <t>G1需2，G2需5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>各组的高峰时段相互重叠，不分区时可错峰共用的无人机/电池被“锁定”在各自组内</t>
+          <t>各组的高峰时段相互重叠，不分区时可错峰共用的无人机/电池被“锁定”在各自组内；电池返回后需充电周转（占用至充满），组内峰值被放大</t>
         </is>
       </c>
     </row>
@@ -1776,17 +1776,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>中继无人机</t>
+          <t>C型电池组</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -1796,12 +1796,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>G1需1，G2需2</t>
+          <t>G1需3，G2需2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>同一中继架次同时保障多个组的运输架次，分区后需各组独立派出：Q3-R02(G1/G2)；不同组的中继任务时段重叠，无法再由同一中继实体/组件先后执行</t>
+          <t>各组的高峰时段相互重叠，不分区时可错峰共用的无人机/电池被“锁定”在各自组内；电池返回后需充电周转（占用至充满），组内峰值被放大</t>
         </is>
       </c>
     </row>
@@ -1811,67 +1811,67 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>中继能源组件</t>
+          <t>中继无人机</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>G1需1，G2需2</t>
+          <t>G1需2，G2需2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>同一中继架次同时保障多个组的运输架次，分区后需各组独立派出：Q3-R02(G1/G2)；不同组的中继任务时段重叠，无法再由同一中继实体/组件先后执行</t>
+          <t>同一中继架次同时保障多个组的运输架次，分区后需各组独立派出：Q3-R01(G1/G2)、Q3-R02(G1/G2)；不同组的中继任务时段重叠，无法再由同一中继实体/组件先后执行</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A型运输无人机</t>
+          <t>中继能源组件</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
         <v>6</v>
       </c>
-      <c r="E7" t="n">
-        <v>4</v>
-      </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>G1需4，G2需2</t>
+          <t>G1需3，G2需2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>各组的高峰时段相互重叠，不分区时可错峰共用的无人机/电池被“锁定”在各自组内</t>
+          <t>同一中继架次同时保障多个组的运输架次，分区后需各组独立派出：Q3-R01(G1/G2)、Q3-R02(G1/G2)；不同组的中继任务时段重叠，无法再由同一中继实体/组件先后执行</t>
         </is>
       </c>
     </row>
@@ -1881,27 +1881,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B型运输无人机</t>
+          <t>A型运输无人机</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>G1需1，G3需2</t>
+          <t>G1需3，G2需3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1916,27 +1916,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C型运输无人机</t>
+          <t>B型运输无人机</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>G1需2，G2需1</t>
+          <t>G1需1，G2需1，G3需2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1951,32 +1951,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>中继无人机</t>
+          <t>C型运输无人机</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>G1需1，G2需2，G3需2</t>
+          <t>G1需2，G2需1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>同一中继架次同时保障多个组的运输架次，分区后需各组独立派出：Q3-R02(G1/G2/G3)、Q3-R01(G2/G3)；不同组的中继任务时段重叠，无法再由同一中继实体/组件先后执行</t>
+          <t>各组的高峰时段相互重叠，不分区时可错峰共用的无人机/电池被“锁定”在各自组内</t>
         </is>
       </c>
     </row>
@@ -1986,30 +1986,135 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>中继能源组件</t>
+          <t>B型电池组</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
       </c>
       <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>G1需1，G2需1，G3需3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>各组的高峰时段相互重叠，不分区时可错峰共用的无人机/电池被“锁定”在各自组内；电池返回后需充电周转（占用至充满），组内峰值被放大</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>C型电池组</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>G1需3，G2需2</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>各组的高峰时段相互重叠，不分区时可错峰共用的无人机/电池被“锁定”在各自组内；电池返回后需充电周转（占用至充满），组内峰值被放大</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>中继无人机</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>G1需1，G2需2，G3需2</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>同一中继架次同时保障多个组的运输架次，分区后需各组独立派出：Q3-R02(G1/G2/G3)、Q3-R01(G2/G3)；不同组的中继任务时段重叠，无法再由同一中继实体/组件先后执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>中继能源组件</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
         <v>6</v>
       </c>
-      <c r="F11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="E14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>G1需1，G2需2，G3需2</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>G1需1，G2需3，G3需2</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>同一中继架次同时保障多个组的运输架次，分区后需各组独立派出：Q3-R02(G1/G2/G3)、Q3-R01(G2/G3)；不同组的中继任务时段重叠，无法再由同一中继实体/组件先后执行</t>
         </is>
@@ -2074,13 +2179,13 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>2.83</v>
+        <v>2.791</v>
       </c>
     </row>
     <row r="3">
@@ -2093,16 +2198,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>4.173</v>
+        <v>5.116</v>
       </c>
     </row>
     <row r="4">
@@ -2115,16 +2220,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>3.942</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="5">
@@ -2140,13 +2245,13 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>6.51</v>
+        <v>6.341</v>
       </c>
     </row>
     <row r="6">
@@ -2162,13 +2267,13 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>4.895</v>
+        <v>5.719</v>
       </c>
     </row>
   </sheetData>
@@ -2240,26 +2345,26 @@
         <v>0.05</v>
       </c>
       <c r="C2" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0018</v>
       </c>
       <c r="H2" t="n">
-        <v>1.016</v>
+        <v>1.004</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S009,S011,S015 | S002,S004,S008,S010,S012,S013,S014</t>
+          <t>S001,S002,S004,S005,S009,S010,S013 | S003,S006,S007,S008,S011,S012,S014,S015</t>
         </is>
       </c>
     </row>
@@ -2271,26 +2376,26 @@
         <v>0.1</v>
       </c>
       <c r="C3" t="n">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0643</v>
+        <v>0.0018</v>
       </c>
       <c r="H3" t="n">
-        <v>1.138</v>
+        <v>1.004</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S011,S015 | S002,S004,S008,S009,S010,S012,S013,S014</t>
+          <t>S001,S002,S004,S005,S009,S010,S013 | S003,S006,S007,S008,S011,S012,S014,S015</t>
         </is>
       </c>
     </row>
@@ -2302,26 +2407,26 @@
         <v>0.15</v>
       </c>
       <c r="C4" t="n">
-        <v>165</v>
+        <v>98</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0643</v>
+        <v>0.1082</v>
       </c>
       <c r="H4" t="n">
-        <v>1.138</v>
+        <v>1.243</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S011,S015 | S002,S004,S008,S009,S010,S012,S013,S014</t>
+          <t>S001,S004,S005,S006,S007,S010 | S002,S003,S008,S009,S011,S012,S013,S014,S015</t>
         </is>
       </c>
     </row>
@@ -2333,26 +2438,26 @@
         <v>0.2</v>
       </c>
       <c r="C5" t="n">
-        <v>209</v>
+        <v>122</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0643</v>
+        <v>0.1082</v>
       </c>
       <c r="H5" t="n">
-        <v>1.138</v>
+        <v>1.243</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S011,S015 | S002,S004,S008,S009,S010,S012,S013,S014</t>
+          <t>S001,S004,S005,S006,S007,S010 | S002,S003,S008,S009,S011,S012,S013,S014,S015</t>
         </is>
       </c>
     </row>
@@ -2364,26 +2469,26 @@
         <v>0.3</v>
       </c>
       <c r="C6" t="n">
-        <v>317</v>
+        <v>170</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2903</v>
+        <v>0.1082</v>
       </c>
       <c r="H6" t="n">
-        <v>1.818</v>
+        <v>1.243</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S006,S007,S011,S013 | S008,S009,S010,S012,S014,S015</t>
+          <t>S001,S004,S005,S006,S007,S010 | S002,S003,S008,S009,S011,S012,S013,S014,S015</t>
         </is>
       </c>
     </row>
@@ -2395,26 +2500,26 @@
         <v>0.4</v>
       </c>
       <c r="C7" t="n">
-        <v>399</v>
+        <v>205</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3525</v>
+        <v>0.1082</v>
       </c>
       <c r="H7" t="n">
-        <v>2.089</v>
+        <v>1.243</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S006,S007,S011,S013,S015 | S008,S009,S010,S012,S014</t>
+          <t>S001,S004,S005,S006,S007,S010 | S002,S003,S008,S009,S011,S012,S013,S014,S015</t>
         </is>
       </c>
     </row>
@@ -2426,26 +2531,26 @@
         <v>0.6</v>
       </c>
       <c r="C8" t="n">
-        <v>489</v>
+        <v>240</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3525</v>
+        <v>0.405</v>
       </c>
       <c r="H8" t="n">
-        <v>2.089</v>
+        <v>2.361</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S006,S007,S011,S013,S015 | S008,S009,S010,S012,S014</t>
+          <t>S001,S002,S003,S004,S005,S006,S007,S009,S011,S013,S015 | S008,S010,S012,S014</t>
         </is>
       </c>
     </row>
@@ -2459,26 +2564,26 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>511</v>
+        <v>255</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>30</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7635</v>
+        <v>0.7873</v>
       </c>
       <c r="H9" t="n">
-        <v>7.455</v>
+        <v>8.401999999999999</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S006,S007,S008,S009,S010,S011,S012,S013,S014 | S015</t>
+          <t>S001,S002,S003,S004,S005,S006,S007,S008,S009,S010,S011,S012,S013,S015 | S014</t>
         </is>
       </c>
     </row>
@@ -2490,26 +2595,26 @@
         <v>0.05</v>
       </c>
       <c r="C10" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0321</v>
+        <v>0.0322</v>
       </c>
       <c r="H10" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>S001,S005,S006,S011,S015 | S002,S004,S009,S012,S013 | S003,S007,S008,S010,S014</t>
+          <t>S001,S003,S006,S007,S011,S015 | S002,S008,S009,S010,S013 | S004,S005,S012,S014</t>
         </is>
       </c>
     </row>
@@ -2521,26 +2626,26 @@
         <v>0.1</v>
       </c>
       <c r="C11" t="n">
-        <v>373</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G11" t="n">
-        <v>0.097</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>1.258</v>
+        <v>1.243</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>S001,S005,S006,S011,S015 | S002,S003,S004,S007,S013 | S008,S009,S010,S012,S014</t>
+          <t>S001,S004,S005,S006,S007 | S002,S009,S010,S012,S013,S014 | S003,S008,S011,S015</t>
         </is>
       </c>
     </row>
@@ -2552,26 +2657,26 @@
         <v>0.15</v>
       </c>
       <c r="C12" t="n">
-        <v>853</v>
+        <v>343</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.097</v>
+        <v>0.1377</v>
       </c>
       <c r="H12" t="n">
-        <v>1.258</v>
+        <v>1.406</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>S001,S005,S006,S011,S015 | S002,S003,S004,S007,S013 | S008,S009,S010,S012,S014</t>
+          <t>S001,S003,S006,S007,S011,S015 | S002,S004,S005,S009,S013 | S008,S010,S012,S014</t>
         </is>
       </c>
     </row>
@@ -2583,26 +2688,26 @@
         <v>0.2</v>
       </c>
       <c r="C13" t="n">
-        <v>1449</v>
+        <v>591</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1563</v>
+        <v>0.1982</v>
       </c>
       <c r="H13" t="n">
-        <v>1.387</v>
+        <v>1.641</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S011,S015 | S002,S004,S013 | S008,S009,S010,S012,S014</t>
+          <t>S001,S003,S006,S007,S011,S015 | S002,S004,S005,S009,S010,S013 | S008,S012,S014</t>
         </is>
       </c>
     </row>
@@ -2614,26 +2719,26 @@
         <v>0.3</v>
       </c>
       <c r="C14" t="n">
-        <v>3254</v>
+        <v>1216</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1563</v>
+        <v>0.1982</v>
       </c>
       <c r="H14" t="n">
-        <v>1.387</v>
+        <v>1.641</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S011,S015 | S002,S004,S013 | S008,S009,S010,S012,S014</t>
+          <t>S001,S003,S006,S007,S011,S015 | S002,S004,S005,S009,S010,S013 | S008,S012,S014</t>
         </is>
       </c>
     </row>
@@ -2645,26 +2750,26 @@
         <v>0.4</v>
       </c>
       <c r="C15" t="n">
-        <v>5239</v>
+        <v>1727</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1563</v>
+        <v>0.3643</v>
       </c>
       <c r="H15" t="n">
-        <v>1.387</v>
+        <v>2.414</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S011,S015 | S002,S004,S013 | S008,S009,S010,S012,S014</t>
+          <t>S001,S003,S004,S005,S006,S007,S011,S015 | S002,S009,S013 | S008,S010,S012,S014</t>
         </is>
       </c>
     </row>
@@ -2676,26 +2781,26 @@
         <v>0.6</v>
       </c>
       <c r="C16" t="n">
-        <v>8366</v>
+        <v>2675</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>3.384</v>
+        <v>3.864</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S006,S007,S011,S013,S015 | S008,S010,S014 | S009,S012</t>
+          <t>S001,S002,S003,S004,S005,S009,S011,S013,S015 | S006,S007 | S008,S010,S012,S014</t>
         </is>
       </c>
     </row>
@@ -2709,26 +2814,26 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9330</v>
+        <v>3025</v>
       </c>
       <c r="D17" t="n">
         <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F17" t="n">
         <v>7</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9809</v>
+        <v>0.8699</v>
       </c>
       <c r="H17" t="n">
-        <v>8.528</v>
+        <v>7.53</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S006,S007,S008,S009,S010,S011,S013,S014 | S012 | S015</t>
+          <t>S001,S002,S003,S004,S005,S008,S009,S010,S011,S012,S013,S015 | S006,S007 | S014</t>
         </is>
       </c>
     </row>
@@ -2802,23 +2907,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S011,S015 | S002,S004,S008,S009,S010,S012,S013,S014</t>
+          <t>S001,S004,S005,S006,S007,S010 | S002,S003,S008,S009,S011,S012,S013,S014,S015</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0643</v>
+        <v>0.1082</v>
       </c>
       <c r="H2" t="n">
-        <v>1.138</v>
+        <v>1.243</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>
@@ -2833,26 +2938,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S009,S011 | S002,S004,S008,S010,S012,S013,S014,S015</t>
+          <t>S001,S002,S004,S005,S009,S010,S013 | S003,S006,S007,S008,S011,S012,S014,S015</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0741</v>
+        <v>0.0018</v>
       </c>
       <c r="H3" t="n">
-        <v>1.16</v>
+        <v>1.004</v>
       </c>
       <c r="I3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2864,23 +2969,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S011 | S002,S004,S008,S009,S010,S012,S013,S014,S015</t>
+          <t>S001,S004,S005,S006,S007,S012,S014 | S002,S003,S008,S009,S010,S011,S013,S015</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1305</v>
+        <v>0.0319</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3</v>
+        <v>1.066</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -2895,23 +3000,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S005,S006,S007,S011,S013 | S004,S008,S009,S010,S012,S014,S015</t>
+          <t>S001,S004,S005,S006,S007,S010,S014 | S002,S003,S008,S009,S011,S012,S013,S015</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1483</v>
+        <v>0.0445</v>
       </c>
       <c r="H5" t="n">
-        <v>1.348</v>
+        <v>1.093</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -2926,23 +3031,23 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S006,S011,S013,S015 | S003,S007,S008,S009,S010,S012,S014</t>
+          <t>S001,S004,S005,S006,S007,S008,S010,S012 | S002,S003,S009,S011,S013,S014,S015</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1717</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>1.415</v>
+        <v>1.196</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -2957,23 +3062,23 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>S001,S005,S006,S008,S009,S010,S011,S012,S014,S015 | S002,S003,S004,S007,S013</t>
+          <t>S001,S004,S005,S006,S007,S012 | S002,S003,S008,S009,S010,S011,S013,S014,S015</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1856</v>
+        <v>0.0956</v>
       </c>
       <c r="H7" t="n">
-        <v>1.456</v>
+        <v>1.211</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -2988,26 +3093,26 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S009,S011,S015 | S002,S004,S008,S010,S012,S013,S014</t>
+          <t>S001,S004,S005,S006,S007,S014 | S002,S003,S008,S009,S010,S011,S012,S013,S015</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0975</v>
       </c>
       <c r="H8" t="n">
-        <v>1.016</v>
+        <v>1.216</v>
       </c>
       <c r="I8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3019,23 +3124,23 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>S001,S002,S005,S006,S011,S013,S015 | S003,S004,S007,S008,S009,S010,S012,S014</t>
+          <t>S001,S003,S006,S007,S008,S011,S012,S014,S015 | S002,S004,S005,S009,S010,S013</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="n">
         <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0297</v>
+        <v>0.1105</v>
       </c>
       <c r="H9" t="n">
-        <v>1.061</v>
+        <v>1.249</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
@@ -3050,23 +3155,23 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S010,S011,S015 | S002,S004,S008,S009,S012,S013,S014</t>
+          <t>S001,S004,S005,S006,S007,S008,S010,S012,S014 | S002,S003,S009,S011,S013,S015</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F10" t="n">
         <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>0.053</v>
+        <v>0.1531</v>
       </c>
       <c r="H10" t="n">
-        <v>1.112</v>
+        <v>1.362</v>
       </c>
       <c r="I10" t="b">
         <v>0</v>
@@ -3081,23 +3186,23 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S011,S014,S015 | S002,S004,S008,S009,S010,S012,S013</t>
+          <t>S001,S003,S004,S005,S006,S007,S011,S015 | S002,S008,S009,S010,S012,S013,S014</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" t="n">
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.0644</v>
       </c>
       <c r="H11" t="n">
-        <v>1.136</v>
+        <v>1.138</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
@@ -3112,23 +3217,23 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S011,S015 | S002,S004,S013 | S008,S009,S010,S012,S014</t>
+          <t>S001,S003,S006,S007,S011,S015 | S002,S004,S005,S009,S010,S013 | S008,S012,S014</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1563</v>
+        <v>0.1982</v>
       </c>
       <c r="H12" t="n">
-        <v>1.387</v>
+        <v>1.641</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
@@ -3143,23 +3248,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>S001,S005,S006,S011,S015 | S002,S003,S004,S007,S013 | S008,S009,S010,S012,S014</t>
+          <t>S001,S003,S006,S007,S011,S015 | S002,S004,S005,S009,S013 | S008,S010,S012,S014</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>0.097</v>
+        <v>0.1377</v>
       </c>
       <c r="H13" t="n">
-        <v>1.258</v>
+        <v>1.406</v>
       </c>
       <c r="I13" t="b">
         <v>1</v>
@@ -3174,23 +3279,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S011 | S002,S004,S013 | S008,S009,S010,S012,S014,S015</t>
+          <t>S001,S004,S005,S006,S007 | S002,S003,S009,S011,S013,S015 | S008,S010,S012,S014</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1044</v>
+        <v>0.144</v>
       </c>
       <c r="H14" t="n">
-        <v>1.289</v>
+        <v>1.423</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -3205,26 +3310,26 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S009,S011 | S002,S004,S013 | S008,S010,S012,S014,S015</t>
+          <t>S001,S004,S005,S010 | S002,S009,S012,S013,S014 | S003,S006,S007,S008,S011,S015</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1477</v>
+        <v>0.134</v>
       </c>
       <c r="H15" t="n">
-        <v>1.373</v>
+        <v>1.367</v>
       </c>
       <c r="I15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3236,26 +3341,26 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>S001,S005,S006,S009,S011 | S002,S003,S004,S007,S013 | S008,S010,S012,S014,S015</t>
+          <t>S001,S003,S008,S011,S015 | S002,S009,S012,S013,S014 | S004,S005,S006,S007,S010</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0945</v>
+        <v>0.1487</v>
       </c>
       <c r="H16" t="n">
-        <v>1.24</v>
+        <v>1.448</v>
       </c>
       <c r="I16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3267,23 +3372,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S011 | S002,S004,S013,S015 | S008,S009,S010,S012,S014</t>
+          <t>S001,S003,S006,S007,S008,S011,S015 | S002,S009,S012,S013,S014 | S004,S005,S010</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0989</v>
+        <v>0.197</v>
       </c>
       <c r="H17" t="n">
-        <v>1.261</v>
+        <v>1.568</v>
       </c>
       <c r="I17" t="b">
         <v>0</v>
@@ -3298,23 +3403,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>S001,S005,S006,S011 | S002,S003,S004,S007,S013 | S008,S009,S010,S012,S014,S015</t>
+          <t>S001,S008,S012,S014 | S002,S004,S005,S009,S010,S013 | S003,S006,S007,S011,S015</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F18" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1016</v>
+        <v>0.1734</v>
       </c>
       <c r="H18" t="n">
-        <v>1.28</v>
+        <v>1.465</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
@@ -3329,23 +3434,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>S001,S005,S006,S011,S015 | S002,S004,S013 | S003,S007,S008,S009,S010,S012,S014</t>
+          <t>S001,S003,S008,S011,S015 | S002,S004,S005,S009,S010,S013 | S006,S007,S012,S014</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F19" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1125</v>
+        <v>0.1798</v>
       </c>
       <c r="H19" t="n">
-        <v>1.307</v>
+        <v>1.529</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
@@ -3360,23 +3465,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S011 | S002,S004,S010,S013,S015 | S008,S009,S012,S014</t>
+          <t>S001,S002,S009,S013 | S003,S008,S011,S012,S014,S015 | S004,S005,S006,S007,S010</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G20" t="n">
-        <v>0.129</v>
+        <v>0.1917</v>
       </c>
       <c r="H20" t="n">
-        <v>1.374</v>
+        <v>1.595</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
@@ -3391,23 +3496,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S011 | S002,S004,S009,S012,S013 | S008,S010,S014,S015</t>
+          <t>S001,S003,S011,S015 | S002,S004,S005,S009,S010,S013 | S006,S007,S008,S012,S014</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1317</v>
+        <v>0.197</v>
       </c>
       <c r="H21" t="n">
-        <v>1.381</v>
+        <v>1.635</v>
       </c>
       <c r="I21" t="b">
         <v>0</v>
@@ -3424,7 +3529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3480,7 +3585,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Q3-T02</t>
+          <t>Q3-T03</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3492,7 +3597,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1312.5</v>
+        <v>1312.6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -3516,7 +3621,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Q3-T04</t>
+          <t>Q3-T10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3525,14 +3630,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1312.7</v>
       </c>
       <c r="F3" t="n">
-        <v>1312.6</v>
+        <v>2625.3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>G1-A2</t>
+          <t>G1-A1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -3552,7 +3657,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Q3-T09</t>
+          <t>Q3-T17</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3561,10 +3666,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312.5</v>
+        <v>2697.2</v>
       </c>
       <c r="F4" t="n">
-        <v>2565</v>
+        <v>4393</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -3573,7 +3678,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>G1-AB3</t>
+          <t>G1-AB1</t>
         </is>
       </c>
     </row>
@@ -3588,28 +3693,28 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Q3-T10</t>
+          <t>Q3-T09</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A型运输</t>
+          <t>B型运输</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312.6</v>
+        <v>1126.7</v>
       </c>
       <c r="F5" t="n">
-        <v>2565.1</v>
+        <v>2681.3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>G1-A2</t>
+          <t>G1-B1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>G1-AB4</t>
+          <t>G1-BB1</t>
         </is>
       </c>
     </row>
@@ -3624,28 +3729,28 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Q3-T14</t>
+          <t>Q3-T21</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A型运输</t>
+          <t>B型运输</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2178.8</v>
+        <v>4587.3</v>
       </c>
       <c r="F6" t="n">
-        <v>3399.4</v>
+        <v>6513.1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>G1-A3</t>
+          <t>G1-B1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>G1-AB1</t>
+          <t>G1-BB1</t>
         </is>
       </c>
     </row>
@@ -3660,28 +3765,28 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Q3-T16</t>
+          <t>Q3-T07</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A型运输</t>
+          <t>C型运输</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2466.8</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>4475</v>
+        <v>1561.4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>G1-A4</t>
+          <t>G1-C1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>G1-AB2</t>
+          <t>G1-CB1</t>
         </is>
       </c>
     </row>
@@ -3696,28 +3801,28 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Q3-T12</t>
+          <t>Q3-T08</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B型运输</t>
+          <t>C型运输</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1868.6</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>3019</v>
+        <v>1627.4</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>G1-B1</t>
+          <t>G1-C2</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>G1-BB1</t>
+          <t>G1-CB2</t>
         </is>
       </c>
     </row>
@@ -3732,28 +3837,28 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Q3-T21</t>
+          <t>Q3-T11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B型运输</t>
+          <t>C型运输</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4924.9</v>
+        <v>1561.5</v>
       </c>
       <c r="F9" t="n">
-        <v>6754.5</v>
+        <v>3975.3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>G1-B1</t>
+          <t>G1-C1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>G1-BB1</t>
+          <t>G1-CB3</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3873,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Q3-T07</t>
+          <t>Q3-T19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3777,14 +3882,14 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>3804.6</v>
       </c>
       <c r="F10" t="n">
-        <v>2257.3</v>
+        <v>6522.4</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>G1-C1</t>
+          <t>G1-C2</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3804,28 +3909,28 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-R01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C型运输</t>
+          <t>中继@P1</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2111</v>
+        <v>59</v>
       </c>
       <c r="F11" t="n">
-        <v>4804.4</v>
+        <v>3969.5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>G1-C2</t>
+          <t>G1-R1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>G1-CB2</t>
+          <t>G1-M1</t>
         </is>
       </c>
     </row>
@@ -3840,28 +3945,28 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-R02</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C型运输</t>
+          <t>中继@P2</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2257.3</v>
+        <v>2128.6</v>
       </c>
       <c r="F12" t="n">
-        <v>4500.8</v>
+        <v>6450.4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>G1-C1</t>
+          <t>G1-R2</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>G1-CB3</t>
+          <t>G1-M2</t>
         </is>
       </c>
     </row>
@@ -3876,28 +3981,28 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q3-T19</t>
+          <t>Q3-R03</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C型运输</t>
+          <t>中继@P3</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4500.8</v>
+        <v>4759.2</v>
       </c>
       <c r="F13" t="n">
-        <v>7128.2</v>
+        <v>6560</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>G1-C1</t>
+          <t>G1-R1</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>G1-CB1</t>
+          <t>G1-M3</t>
         </is>
       </c>
     </row>
@@ -3907,33 +4012,33 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-T01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>中继@P4</t>
+          <t>A型运输</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2419.7</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>7130.3</v>
+        <v>1612.1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>G1-R1</t>
+          <t>G2-A1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>G1-M1</t>
+          <t>G2-AB1</t>
         </is>
       </c>
     </row>
@@ -3948,7 +4053,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Q3-T01</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3960,16 +4065,16 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2466.8</v>
+        <v>2678.9</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>G2-A2</t>
+          <t>G2-A3</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>G2-AB2</t>
+          <t>G2-AB3</t>
         </is>
       </c>
     </row>
@@ -3984,7 +4089,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Q3-T03</t>
+          <t>Q3-T04</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3996,16 +4101,16 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1612.1</v>
+        <v>1691.6</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>G2-A1</t>
+          <t>G2-A2</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>G2-AB1</t>
+          <t>G2-AB2</t>
         </is>
       </c>
     </row>
@@ -4020,28 +4125,28 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Q3-T05</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B型运输</t>
+          <t>A型运输</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1612.1</v>
       </c>
       <c r="F17" t="n">
-        <v>1868.6</v>
+        <v>4459.3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>G2-B2</t>
+          <t>G2-A1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>G2-BB2</t>
+          <t>G2-AB4</t>
         </is>
       </c>
     </row>
@@ -4056,28 +4161,28 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Q3-T06</t>
+          <t>Q3-T15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B型运输</t>
+          <t>A型运输</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>2191</v>
       </c>
       <c r="F18" t="n">
-        <v>1554.6</v>
+        <v>4161.3</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>G2-B1</t>
+          <t>G2-A2</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>G2-BB1</t>
+          <t>G2-AB5</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4197,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Q3-T11</t>
+          <t>Q3-T05</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4101,19 +4206,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1554.6</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>3478.5</v>
+        <v>1923.9</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>G2-B1</t>
+          <t>G2-B2</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>G2-BB3</t>
+          <t>G2-BB2</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4233,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Q3-T17</t>
+          <t>Q3-T06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4137,14 +4242,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3019</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>4924.9</v>
+        <v>1126.7</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>G2-B2</t>
+          <t>G2-B1</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -4164,7 +4269,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Q3-T18</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4173,10 +4278,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3478.5</v>
+        <v>1923.9</v>
       </c>
       <c r="F21" t="n">
-        <v>5444.4</v>
+        <v>3792.5</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -4185,7 +4290,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>G2-BB2</t>
+          <t>G2-BB3</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4305,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Q3-T22</t>
+          <t>Q3-T16</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4209,19 +4314,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5444.4</v>
+        <v>2681.3</v>
       </c>
       <c r="F22" t="n">
-        <v>7005.2</v>
+        <v>4587.2</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>G2-B1</t>
+          <t>G2-B2</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>G2-BB3</t>
+          <t>G2-BB1</t>
         </is>
       </c>
     </row>
@@ -4236,28 +4341,28 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Q3-T08</t>
+          <t>Q3-T18</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>C型运输</t>
+          <t>B型运输</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>3792.5</v>
       </c>
       <c r="F23" t="n">
-        <v>2111</v>
+        <v>5758.4</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>G2-C1</t>
+          <t>G2-B1</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>G2-CB1</t>
+          <t>G2-BB2</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4377,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Q3-T20</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4281,10 +4386,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4804.4</v>
+        <v>1627.5</v>
       </c>
       <c r="F24" t="n">
-        <v>7109.6</v>
+        <v>3804.5</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -4308,28 +4413,28 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-T20</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>中继@P1</t>
+          <t>C型运输</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>64.3</v>
+        <v>3975.3</v>
       </c>
       <c r="F25" t="n">
-        <v>3632.2</v>
+        <v>6477.2</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>G2-R1</t>
+          <t>G2-C1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>G2-M1</t>
+          <t>G2-CB2</t>
         </is>
       </c>
     </row>
@@ -4344,28 +4449,28 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R01</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>中继@P4</t>
+          <t>中继@P1</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2419.7</v>
+        <v>59</v>
       </c>
       <c r="F26" t="n">
-        <v>7130.3</v>
+        <v>3969.5</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>G2-R2</t>
+          <t>G2-R1</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>G2-M2</t>
+          <t>G2-M1</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4485,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R02</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4389,19 +4494,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5261.8</v>
+        <v>2128.6</v>
       </c>
       <c r="F27" t="n">
-        <v>7136.8</v>
+        <v>6450.4</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>G2-R1</t>
+          <t>G2-R2</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>G2-M1</t>
+          <t>G2-M2</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4521,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Q3-T02</t>
+          <t>Q3-T03</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4428,7 +4533,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1312.5</v>
+        <v>1312.6</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -4452,7 +4557,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Q3-T04</t>
+          <t>Q3-T10</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4461,14 +4566,14 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1312.7</v>
       </c>
       <c r="F29" t="n">
-        <v>1312.6</v>
+        <v>2625.3</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>G1-A2</t>
+          <t>G1-A1</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4488,7 +4593,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Q3-T09</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4497,14 +4602,14 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312.5</v>
+        <v>1612.1</v>
       </c>
       <c r="F30" t="n">
-        <v>2565</v>
+        <v>4459.3</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>G1-A1</t>
+          <t>G1-A2</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4524,7 +4629,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Q3-T10</t>
+          <t>Q3-T15</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4533,19 +4638,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312.6</v>
+        <v>2191</v>
       </c>
       <c r="F31" t="n">
-        <v>2565.1</v>
+        <v>4161.3</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>G1-A2</t>
+          <t>G1-A3</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>G1-AB4</t>
+          <t>G1-AB1</t>
         </is>
       </c>
     </row>
@@ -4560,28 +4665,28 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Q3-T14</t>
+          <t>Q3-T06</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>A型运输</t>
+          <t>B型运输</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2178.8</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>3399.4</v>
+        <v>1126.7</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>G1-A3</t>
+          <t>G1-B1</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>G1-AB1</t>
+          <t>G1-BB1</t>
         </is>
       </c>
     </row>
@@ -4596,28 +4701,28 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Q3-T16</t>
+          <t>Q3-T07</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>A型运输</t>
+          <t>C型运输</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2466.8</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>4475</v>
+        <v>1561.4</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>G1-A4</t>
+          <t>G1-C1</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>G1-AB2</t>
+          <t>G1-CB1</t>
         </is>
       </c>
     </row>
@@ -4632,28 +4737,28 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Q3-T12</t>
+          <t>Q3-T08</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>B型运输</t>
+          <t>C型运输</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1868.6</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>3019</v>
+        <v>1627.4</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>G1-B1</t>
+          <t>G1-C2</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>G1-BB1</t>
+          <t>G1-CB2</t>
         </is>
       </c>
     </row>
@@ -4668,28 +4773,28 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Q3-T21</t>
+          <t>Q3-T11</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>B型运输</t>
+          <t>C型运输</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4924.9</v>
+        <v>1561.5</v>
       </c>
       <c r="F35" t="n">
-        <v>6754.5</v>
+        <v>3975.3</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>G1-B1</t>
+          <t>G1-C1</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>G1-BB1</t>
+          <t>G1-CB3</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4809,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Q3-T07</t>
+          <t>Q3-T20</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4713,10 +4818,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>3975.3</v>
       </c>
       <c r="F36" t="n">
-        <v>2257.3</v>
+        <v>6477.2</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4740,28 +4845,28 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-R02</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>C型运输</t>
+          <t>中继@P2</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2111</v>
+        <v>2128.6</v>
       </c>
       <c r="F37" t="n">
-        <v>4804.4</v>
+        <v>6450.4</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>G1-C2</t>
+          <t>G1-R1</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>G1-CB2</t>
+          <t>G1-M1</t>
         </is>
       </c>
     </row>
@@ -4771,33 +4876,33 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T01</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>C型运输</t>
+          <t>A型运输</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2257.3</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>4500.8</v>
+        <v>1612.1</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>G1-C1</t>
+          <t>G2-A1</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>G1-CB3</t>
+          <t>G2-AB1</t>
         </is>
       </c>
     </row>
@@ -4807,33 +4912,33 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Q3-T19</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>C型运输</t>
+          <t>A型运输</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4500.8</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>7128.2</v>
+        <v>2678.9</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>G1-C1</t>
+          <t>G2-A3</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>G1-CB1</t>
+          <t>G2-AB3</t>
         </is>
       </c>
     </row>
@@ -4843,33 +4948,33 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-T04</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>中继@P4</t>
+          <t>A型运输</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2419.7</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>7130.3</v>
+        <v>1691.6</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>G1-R1</t>
+          <t>G2-A2</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>G1-M1</t>
+          <t>G2-AB2</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4989,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Q3-T01</t>
+          <t>Q3-T17</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4893,19 +4998,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>2697.2</v>
       </c>
       <c r="F41" t="n">
-        <v>2466.8</v>
+        <v>4393</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>G2-A2</t>
+          <t>G2-A1</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>G2-AB2</t>
+          <t>G2-AB1</t>
         </is>
       </c>
     </row>
@@ -4920,28 +5025,28 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Q3-T03</t>
+          <t>Q3-T09</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>A型运输</t>
+          <t>B型运输</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1126.7</v>
       </c>
       <c r="F42" t="n">
-        <v>1612.1</v>
+        <v>2681.3</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>G2-A1</t>
+          <t>G2-B1</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>G2-AB1</t>
+          <t>G2-BB1</t>
         </is>
       </c>
     </row>
@@ -4956,28 +5061,28 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Q3-T08</t>
+          <t>Q3-T21</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>C型运输</t>
+          <t>B型运输</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>4587.3</v>
       </c>
       <c r="F43" t="n">
-        <v>2111</v>
+        <v>6513.1</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>G2-C1</t>
+          <t>G2-B1</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>G2-CB1</t>
+          <t>G2-BB1</t>
         </is>
       </c>
     </row>
@@ -4992,7 +5097,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Q3-T20</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5001,10 +5106,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4804.4</v>
+        <v>1627.5</v>
       </c>
       <c r="F44" t="n">
-        <v>7109.6</v>
+        <v>3804.5</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -5028,28 +5133,28 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-T19</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>中继@P1</t>
+          <t>C型运输</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>64.3</v>
+        <v>3804.6</v>
       </c>
       <c r="F45" t="n">
-        <v>3632.2</v>
+        <v>6522.4</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>G2-R1</t>
+          <t>G2-C1</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>G2-M1</t>
+          <t>G2-CB2</t>
         </is>
       </c>
     </row>
@@ -5064,28 +5169,28 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R01</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>中继@P4</t>
+          <t>中继@P1</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2419.7</v>
+        <v>59</v>
       </c>
       <c r="F46" t="n">
-        <v>7130.3</v>
+        <v>3969.5</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>G2-R2</t>
+          <t>G2-R1</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>G2-M2</t>
+          <t>G2-M1</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5205,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R02</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5109,19 +5214,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5261.8</v>
+        <v>2128.6</v>
       </c>
       <c r="F47" t="n">
-        <v>7136.8</v>
+        <v>6450.4</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>G2-R1</t>
+          <t>G2-R2</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>G2-M1</t>
+          <t>G2-M2</t>
         </is>
       </c>
     </row>
@@ -5131,33 +5236,33 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Q3-T05</t>
+          <t>Q3-R03</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>B型运输</t>
+          <t>中继@P3</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>4759.2</v>
       </c>
       <c r="F48" t="n">
-        <v>1868.6</v>
+        <v>6560</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>G3-B2</t>
+          <t>G2-R1</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>G3-BB2</t>
+          <t>G2-M3</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5277,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Q3-T06</t>
+          <t>Q3-T05</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5184,7 +5289,7 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>1554.6</v>
+        <v>1923.9</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -5208,7 +5313,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Q3-T11</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5217,10 +5322,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1554.6</v>
+        <v>1923.9</v>
       </c>
       <c r="F50" t="n">
-        <v>3478.5</v>
+        <v>3792.5</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -5229,7 +5334,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>G3-BB3</t>
+          <t>G3-BB2</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5349,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Q3-T17</t>
+          <t>Q3-T16</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5253,10 +5358,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3019</v>
+        <v>2681.3</v>
       </c>
       <c r="F51" t="n">
-        <v>4924.9</v>
+        <v>4587.2</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -5265,7 +5370,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>G3-BB1</t>
+          <t>G3-BB3</t>
         </is>
       </c>
     </row>
@@ -5289,10 +5394,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3478.5</v>
+        <v>3792.5</v>
       </c>
       <c r="F52" t="n">
-        <v>5444.4</v>
+        <v>5758.4</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -5301,7 +5406,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>G3-BB2</t>
+          <t>G3-BB1</t>
         </is>
       </c>
     </row>
@@ -5316,28 +5421,28 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Q3-T22</t>
+          <t>Q3-R01</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>B型运输</t>
+          <t>中继@P1</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5444.4</v>
+        <v>59</v>
       </c>
       <c r="F53" t="n">
-        <v>7005.2</v>
+        <v>3969.5</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>G3-B1</t>
+          <t>G3-R1</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>G3-BB3</t>
+          <t>G3-M1</t>
         </is>
       </c>
     </row>
@@ -5352,62 +5457,26 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R02</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>中继@P1</t>
+          <t>中继@P2</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>64.3</v>
+        <v>2128.6</v>
       </c>
       <c r="F54" t="n">
-        <v>3632.2</v>
+        <v>6450.4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>G3-R1</t>
+          <t>G3-R2</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
-        <is>
-          <t>G3-M1</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>3</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>中继@P4</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>2419.7</v>
-      </c>
-      <c r="F55" t="n">
-        <v>7130.3</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>G3-R2</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
         <is>
           <t>G3-M2</t>
         </is>
@@ -5424,7 +5493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5452,12 +5521,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S001,S005,S006,S011</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Q3-T02,Q3-T04,Q3-T07,Q3-T09,Q3-T10,Q3-T12,Q3-T14,Q3-T15,Q3-T16</t>
+          <t>Q3-T07,Q3-T08</t>
         </is>
       </c>
     </row>
@@ -5469,12 +5538,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S002,S013</t>
+          <t>S002,S009,S013</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Q3-T01,Q3-T03,Q3-T08</t>
+          <t>Q3-T01,Q3-T02,Q3-T04,Q3-T13</t>
         </is>
       </c>
     </row>
@@ -5486,12 +5555,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S003,S007</t>
+          <t>S003,S011,S015</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Q3-T13,Q3-T19</t>
+          <t>Q3-T06,Q3-T12,Q3-T15,Q3-T20</t>
         </is>
       </c>
     </row>
@@ -5503,12 +5572,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S004,S005</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Q3-T20</t>
+          <t>Q3-T17,Q3-T19,Q3-T21</t>
         </is>
       </c>
     </row>
@@ -5520,12 +5589,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S006,S007</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Q3-T17,Q3-T18</t>
+          <t>Q3-T03,Q3-T10,Q3-T11</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5606,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Q3-T22</t>
+          <t>Q3-T16,Q3-T18</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5628,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Q3-T06</t>
+          <t>Q3-T09</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5645,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Q3-T11</t>
+          <t>Q3-T05</t>
         </is>
       </c>
     </row>
@@ -5593,24 +5662,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Q3-T05</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>块10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>S015</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Q3-T21</t>
+          <t>Q3-T14</t>
         </is>
       </c>
     </row>
